--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N19_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>28.2974384695064</v>
       </c>
       <c r="E2" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F2" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>37.09672382595664</v>
       </c>
       <c r="E3" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F3" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>37.83433308371036</v>
       </c>
       <c r="E4" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F4" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>24.14383060355207</v>
       </c>
       <c r="E5" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F5" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>52.73391063933825</v>
       </c>
       <c r="E6" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F6" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>74.2753189375541</v>
       </c>
       <c r="E7" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F7" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>16.80663612242139</v>
       </c>
       <c r="E8" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F8" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>23.87631467305757</v>
       </c>
       <c r="E9" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F9" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>12.98045156332619</v>
       </c>
       <c r="E10" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F10" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         <v>17.50322579050763</v>
       </c>
       <c r="E11" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F11" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>66.20251434375822</v>
       </c>
       <c r="E12" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F12" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         <v>29.30347738720183</v>
       </c>
       <c r="E13" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F13" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>39.58215717648266</v>
       </c>
       <c r="E14" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F14" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         <v>75.59532248568385</v>
       </c>
       <c r="E15" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F15" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>21.37822163834592</v>
       </c>
       <c r="E16" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F16" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         <v>29.26013201343745</v>
       </c>
       <c r="E17" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F17" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
         <v>67.25716432274555</v>
       </c>
       <c r="E18" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F18" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         <v>32.65821752021431</v>
       </c>
       <c r="E19" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F19" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         <v>46.96809001109095</v>
       </c>
       <c r="E20" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F20" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>78.06276853778559</v>
+        <v>48.70942857045448</v>
       </c>
       <c r="D21" t="n">
-        <v>52.85973067524754</v>
+        <v>14.81883716897927</v>
       </c>
       <c r="E21" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F21" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>28.03879000412563</v>
+        <v>78.06276853778559</v>
       </c>
       <c r="D22" t="n">
-        <v>32.56645939561717</v>
+        <v>52.85973067524754</v>
       </c>
       <c r="E22" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F22" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>14.57867581387934</v>
+        <v>28.03879000412563</v>
       </c>
       <c r="D23" t="n">
-        <v>19.30750632597017</v>
+        <v>32.56645939561717</v>
       </c>
       <c r="E23" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F23" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>39.57820473161166</v>
+        <v>14.57867581387934</v>
       </c>
       <c r="D24" t="n">
-        <v>41.18881886694251</v>
+        <v>19.30750632597017</v>
       </c>
       <c r="E24" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F24" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>48.49442453902507</v>
+        <v>39.57820473161166</v>
       </c>
       <c r="D25" t="n">
-        <v>47.63760868515793</v>
+        <v>41.18881886694251</v>
       </c>
       <c r="E25" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F25" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>40.66319064906257</v>
+        <v>48.49442453902507</v>
       </c>
       <c r="D26" t="n">
-        <v>43.9715389209418</v>
+        <v>47.63760868515793</v>
       </c>
       <c r="E26" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F26" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>60.19989369992467</v>
+        <v>40.66319064906257</v>
       </c>
       <c r="D27" t="n">
-        <v>58.48409851514777</v>
+        <v>43.9715389209418</v>
       </c>
       <c r="E27" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F27" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>41.00386655725673</v>
+        <v>60.19989369992467</v>
       </c>
       <c r="D28" t="n">
-        <v>39.32460811731688</v>
+        <v>58.48409851514777</v>
       </c>
       <c r="E28" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F28" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>24.45673919776452</v>
+        <v>41.00386655725673</v>
       </c>
       <c r="D29" t="n">
-        <v>22.64808634483864</v>
+        <v>39.32460811731688</v>
       </c>
       <c r="E29" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F29" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>41.04987180168215</v>
+        <v>24.45673919776452</v>
       </c>
       <c r="D30" t="n">
-        <v>43.53601092514696</v>
+        <v>22.64808634483864</v>
       </c>
       <c r="E30" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F30" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>29.53165401263367</v>
+        <v>41.04987180168215</v>
       </c>
       <c r="D31" t="n">
-        <v>32.70490890817412</v>
+        <v>43.53601092514696</v>
       </c>
       <c r="E31" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F31" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>51.53710305330144</v>
+        <v>29.53165401263367</v>
       </c>
       <c r="D32" t="n">
-        <v>49.23750825283024</v>
+        <v>32.70490890817412</v>
       </c>
       <c r="E32" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F32" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>52.82039473566915</v>
+        <v>51.53710305330144</v>
       </c>
       <c r="D33" t="n">
-        <v>55.11280875762804</v>
+        <v>49.23750825283024</v>
       </c>
       <c r="E33" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F33" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>33.00310672735583</v>
+        <v>52.82039473566915</v>
       </c>
       <c r="D34" t="n">
-        <v>30.38173552038773</v>
+        <v>55.11280875762804</v>
       </c>
       <c r="E34" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F34" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>12.94234922699788</v>
+        <v>33.00310672735583</v>
       </c>
       <c r="D35" t="n">
-        <v>15.22876688687335</v>
+        <v>30.38173552038773</v>
       </c>
       <c r="E35" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F35" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>24.73564093677289</v>
+        <v>12.94234922699788</v>
       </c>
       <c r="D36" t="n">
-        <v>20.35805849956548</v>
+        <v>15.22876688687335</v>
       </c>
       <c r="E36" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F36" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>71.47574966463512</v>
+        <v>24.73564093677289</v>
       </c>
       <c r="D37" t="n">
-        <v>68.34204434342483</v>
+        <v>20.35805849956548</v>
       </c>
       <c r="E37" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F37" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>63.31761899912053</v>
+        <v>71.47574966463512</v>
       </c>
       <c r="D38" t="n">
-        <v>59.9258603812732</v>
+        <v>68.34204434342483</v>
       </c>
       <c r="E38" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F38" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>33.93601499827309</v>
+        <v>63.31761899912053</v>
       </c>
       <c r="D39" t="n">
-        <v>29.3249140214946</v>
+        <v>59.9258603812732</v>
       </c>
       <c r="E39" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F39" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>39.76165347068428</v>
+        <v>33.93601499827309</v>
       </c>
       <c r="D40" t="n">
-        <v>35.94924212257506</v>
+        <v>29.3249140214946</v>
       </c>
       <c r="E40" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F40" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>38.75169089743346</v>
+        <v>39.76165347068428</v>
       </c>
       <c r="D41" t="n">
-        <v>38.7093690890898</v>
+        <v>35.94924212257506</v>
       </c>
       <c r="E41" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F41" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>58.99845547043221</v>
+        <v>38.75169089743346</v>
       </c>
       <c r="D42" t="n">
-        <v>59.00832238420119</v>
+        <v>38.7093690890898</v>
       </c>
       <c r="E42" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F42" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>25.91168857331724</v>
+        <v>58.99845547043221</v>
       </c>
       <c r="D43" t="n">
-        <v>22.67930427888045</v>
+        <v>59.00832238420119</v>
       </c>
       <c r="E43" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F43" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>40.0523274140572</v>
+        <v>25.91168857331724</v>
       </c>
       <c r="D44" t="n">
-        <v>39.1636962144492</v>
+        <v>22.67930427888045</v>
       </c>
       <c r="E44" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F44" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>30.75313152467118</v>
+        <v>40.0523274140572</v>
       </c>
       <c r="D45" t="n">
-        <v>27.55036616339176</v>
+        <v>39.1636962144492</v>
       </c>
       <c r="E45" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F45" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>33.50411929799861</v>
+        <v>30.75313152467118</v>
       </c>
       <c r="D46" t="n">
-        <v>33.70244511201285</v>
+        <v>27.55036616339176</v>
       </c>
       <c r="E46" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F46" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>42.88348685021136</v>
+        <v>33.50411929799861</v>
       </c>
       <c r="D47" t="n">
-        <v>34.0357070872335</v>
+        <v>33.70244511201285</v>
       </c>
       <c r="E47" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F47" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>45.44894425923547</v>
+        <v>42.88348685021136</v>
       </c>
       <c r="D48" t="n">
-        <v>45.80636902918911</v>
+        <v>34.0357070872335</v>
       </c>
       <c r="E48" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F48" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>52.62482956785848</v>
+        <v>45.44894425923547</v>
       </c>
       <c r="D49" t="n">
-        <v>52.97795930841895</v>
+        <v>45.80636902918911</v>
       </c>
       <c r="E49" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F49" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>22.2047934325612</v>
+        <v>52.62482956785848</v>
       </c>
       <c r="D50" t="n">
-        <v>21.89981582034473</v>
+        <v>52.97795930841895</v>
       </c>
       <c r="E50" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F50" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>81.63413579678436</v>
+        <v>22.2047934325612</v>
       </c>
       <c r="D51" t="n">
-        <v>68.5771988312915</v>
+        <v>21.89981582034473</v>
       </c>
       <c r="E51" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F51" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>36.84874495747128</v>
+        <v>81.63413579678436</v>
       </c>
       <c r="D52" t="n">
-        <v>37.23993736040726</v>
+        <v>68.5771988312915</v>
       </c>
       <c r="E52" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F52" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>85.4958883297631</v>
+        <v>36.84874495747128</v>
       </c>
       <c r="D53" t="n">
-        <v>72.17100268194918</v>
+        <v>37.23993736040726</v>
       </c>
       <c r="E53" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F53" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>22.36122879115752</v>
+        <v>85.4958883297631</v>
       </c>
       <c r="D54" t="n">
-        <v>15.76900801175926</v>
+        <v>72.17100268194918</v>
       </c>
       <c r="E54" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F54" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>9.659380497501726</v>
+        <v>22.36122879115752</v>
       </c>
       <c r="D55" t="n">
-        <v>9.625199503150517</v>
+        <v>15.76900801175926</v>
       </c>
       <c r="E55" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F55" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>24.42735117834011</v>
+        <v>9.659380497501726</v>
       </c>
       <c r="D56" t="n">
-        <v>24.91958584947173</v>
+        <v>9.625199503150517</v>
       </c>
       <c r="E56" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F56" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>21.15231072453556</v>
+        <v>24.42735117834011</v>
       </c>
       <c r="D57" t="n">
-        <v>21.39975713156132</v>
+        <v>24.91958584947173</v>
       </c>
       <c r="E57" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F57" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>5.34286374886876</v>
+        <v>21.15231072453556</v>
       </c>
       <c r="D58" t="n">
-        <v>4.965465384478273</v>
+        <v>21.39975713156132</v>
       </c>
       <c r="E58" t="n">
-        <v>23.75691165727402</v>
+        <v>23.55600329676586</v>
       </c>
       <c r="F58" t="n">
-        <v>17.46473228021168</v>
+        <v>17.57306247170321</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,23 +2304,55 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
+        <v>5.34286374886876</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4.965465384478273</v>
+      </c>
+      <c r="E59" t="n">
+        <v>23.55600329676586</v>
+      </c>
+      <c r="F59" t="n">
+        <v>17.57306247170321</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>T1791L</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>W0035F0002T0006Z000C1N19.png</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="n">
         <v>42.31700742462803</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D60" t="n">
         <v>42.84859715741959</v>
       </c>
-      <c r="E59" t="n">
-        <v>23.75691165727402</v>
-      </c>
-      <c r="F59" t="n">
-        <v>17.46473228021168</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>T1791L</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
+      <c r="E60" t="n">
+        <v>23.55600329676586</v>
+      </c>
+      <c r="F60" t="n">
+        <v>17.57306247170321</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>T1791L</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>92.5713026238766</v>
+        <v>15.04283667637995</v>
       </c>
       <c r="D2" t="n">
-        <v>28.2974384695064</v>
+        <v>4.598333751294789</v>
       </c>
       <c r="E2" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F2" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>85.15437217525991</v>
+        <v>13.83758547847973</v>
       </c>
       <c r="D3" t="n">
-        <v>37.09672382595664</v>
+        <v>6.028217621717955</v>
       </c>
       <c r="E3" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F3" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>83.35762653310552</v>
+        <v>13.54561431162965</v>
       </c>
       <c r="D4" t="n">
-        <v>37.83433308371036</v>
+        <v>6.148079126102934</v>
       </c>
       <c r="E4" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F4" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>90.44689955949934</v>
+        <v>14.69762117841864</v>
       </c>
       <c r="D5" t="n">
-        <v>24.14383060355207</v>
+        <v>3.923372473077212</v>
       </c>
       <c r="E5" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F5" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>83.92390193553166</v>
+        <v>13.6376340645239</v>
       </c>
       <c r="D6" t="n">
-        <v>52.73391063933825</v>
+        <v>8.569260478892465</v>
       </c>
       <c r="E6" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F6" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>91.74018668009204</v>
+        <v>14.90778033551496</v>
       </c>
       <c r="D7" t="n">
-        <v>74.2753189375541</v>
+        <v>12.06973932735254</v>
       </c>
       <c r="E7" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F7" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>76.51795195993422</v>
+        <v>12.43416719348931</v>
       </c>
       <c r="D8" t="n">
-        <v>16.80663612242139</v>
+        <v>2.731078369893476</v>
       </c>
       <c r="E8" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F8" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>81.20074447262007</v>
+        <v>13.19512097680076</v>
       </c>
       <c r="D9" t="n">
-        <v>23.87631467305757</v>
+        <v>3.879901134371855</v>
       </c>
       <c r="E9" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F9" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>66.28427181705619</v>
+        <v>10.77119417027163</v>
       </c>
       <c r="D10" t="n">
-        <v>12.98045156332619</v>
+        <v>2.109323379040505</v>
       </c>
       <c r="E10" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F10" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>54.99507397582273</v>
+        <v>8.936699521071194</v>
       </c>
       <c r="D11" t="n">
-        <v>17.50322579050763</v>
+        <v>2.844274190957491</v>
       </c>
       <c r="E11" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F11" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>70.06992648524681</v>
+        <v>11.38636305385261</v>
       </c>
       <c r="D12" t="n">
-        <v>66.20251434375822</v>
+        <v>10.75790858086071</v>
       </c>
       <c r="E12" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F12" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>71.26270426417997</v>
+        <v>11.58018944292925</v>
       </c>
       <c r="D13" t="n">
-        <v>29.30347738720183</v>
+        <v>4.761815075420297</v>
       </c>
       <c r="E13" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F13" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>81.73045278040274</v>
+        <v>13.28119857681545</v>
       </c>
       <c r="D14" t="n">
-        <v>39.58215717648266</v>
+        <v>6.432100541178433</v>
       </c>
       <c r="E14" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F14" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>77.6840287690206</v>
+        <v>12.62365467496585</v>
       </c>
       <c r="D15" t="n">
-        <v>75.59532248568385</v>
+        <v>12.28423990392363</v>
       </c>
       <c r="E15" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F15" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.68187566868316</v>
+        <v>5.960804796161014</v>
       </c>
       <c r="D16" t="n">
-        <v>21.37822163834592</v>
+        <v>3.473961016231212</v>
       </c>
       <c r="E16" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F16" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>62.91826687531079</v>
+        <v>10.224218367238</v>
       </c>
       <c r="D17" t="n">
-        <v>29.26013201343745</v>
+        <v>4.754771452183586</v>
       </c>
       <c r="E17" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F17" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>67.02587833547899</v>
+        <v>10.89170522951534</v>
       </c>
       <c r="D18" t="n">
-        <v>67.25716432274555</v>
+        <v>10.92928920244615</v>
       </c>
       <c r="E18" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F18" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>38.2680014759972</v>
+        <v>6.218550239849544</v>
       </c>
       <c r="D19" t="n">
-        <v>32.65821752021431</v>
+        <v>5.306960347034827</v>
       </c>
       <c r="E19" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F19" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>74.17026369275115</v>
+        <v>12.05266785007206</v>
       </c>
       <c r="D20" t="n">
-        <v>46.96809001109095</v>
+        <v>7.632314626802279</v>
       </c>
       <c r="E20" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F20" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>48.70942857045448</v>
+        <v>7.915282142698854</v>
       </c>
       <c r="D21" t="n">
-        <v>14.81883716897927</v>
+        <v>2.408061039959132</v>
       </c>
       <c r="E21" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F21" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>78.06276853778559</v>
+        <v>12.68519988739016</v>
       </c>
       <c r="D22" t="n">
-        <v>52.85973067524754</v>
+        <v>8.589706234727725</v>
       </c>
       <c r="E22" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F22" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>28.03879000412563</v>
+        <v>4.556303375670415</v>
       </c>
       <c r="D23" t="n">
-        <v>32.56645939561717</v>
+        <v>5.29204965178779</v>
       </c>
       <c r="E23" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F23" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>14.57867581387934</v>
+        <v>2.369034819755392</v>
       </c>
       <c r="D24" t="n">
-        <v>19.30750632597017</v>
+        <v>3.137469777970153</v>
       </c>
       <c r="E24" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F24" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>39.57820473161166</v>
+        <v>6.431458268886894</v>
       </c>
       <c r="D25" t="n">
-        <v>41.18881886694251</v>
+        <v>6.693183065878158</v>
       </c>
       <c r="E25" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F25" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>48.49442453902507</v>
+        <v>7.880343987591574</v>
       </c>
       <c r="D26" t="n">
-        <v>47.63760868515793</v>
+        <v>7.741111411338164</v>
       </c>
       <c r="E26" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F26" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>40.66319064906257</v>
+        <v>6.607768480472668</v>
       </c>
       <c r="D27" t="n">
-        <v>43.9715389209418</v>
+        <v>7.145375074653042</v>
       </c>
       <c r="E27" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F27" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>60.19989369992467</v>
+        <v>9.78248272623776</v>
       </c>
       <c r="D28" t="n">
-        <v>58.48409851514777</v>
+        <v>9.503666008711512</v>
       </c>
       <c r="E28" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F28" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>41.00386655725673</v>
+        <v>6.663128315554219</v>
       </c>
       <c r="D29" t="n">
-        <v>39.32460811731688</v>
+        <v>6.390248819063993</v>
       </c>
       <c r="E29" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F29" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>24.45673919776452</v>
+        <v>3.974220119636735</v>
       </c>
       <c r="D30" t="n">
-        <v>22.64808634483864</v>
+        <v>3.680314031036279</v>
       </c>
       <c r="E30" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F30" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>41.04987180168215</v>
+        <v>6.67060416777335</v>
       </c>
       <c r="D31" t="n">
-        <v>43.53601092514696</v>
+        <v>7.074601775336381</v>
       </c>
       <c r="E31" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F31" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>29.53165401263367</v>
+        <v>4.798893777052971</v>
       </c>
       <c r="D32" t="n">
-        <v>32.70490890817412</v>
+        <v>5.314547697578295</v>
       </c>
       <c r="E32" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F32" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>51.53710305330144</v>
+        <v>8.374779246161484</v>
       </c>
       <c r="D33" t="n">
-        <v>49.23750825283024</v>
+        <v>8.001095091084913</v>
       </c>
       <c r="E33" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F33" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>52.82039473566915</v>
+        <v>8.583314144546238</v>
       </c>
       <c r="D34" t="n">
-        <v>55.11280875762804</v>
+        <v>8.955831423114557</v>
       </c>
       <c r="E34" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F34" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>33.00310672735583</v>
+        <v>5.363004843195323</v>
       </c>
       <c r="D35" t="n">
-        <v>30.38173552038773</v>
+        <v>4.937032022063006</v>
       </c>
       <c r="E35" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F35" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>12.94234922699788</v>
+        <v>2.103131749387156</v>
       </c>
       <c r="D36" t="n">
-        <v>15.22876688687335</v>
+        <v>2.474674619116919</v>
       </c>
       <c r="E36" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F36" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>24.73564093677289</v>
+        <v>4.019541652225594</v>
       </c>
       <c r="D37" t="n">
-        <v>20.35805849956548</v>
+        <v>3.308184506179391</v>
       </c>
       <c r="E37" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F37" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>71.47574966463512</v>
+        <v>11.61480932050321</v>
       </c>
       <c r="D38" t="n">
-        <v>68.34204434342483</v>
+        <v>11.10558220580654</v>
       </c>
       <c r="E38" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F38" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>63.31761899912053</v>
+        <v>10.28911308735709</v>
       </c>
       <c r="D39" t="n">
-        <v>59.9258603812732</v>
+        <v>9.737952311956896</v>
       </c>
       <c r="E39" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F39" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>33.93601499827309</v>
+        <v>5.514602437219377</v>
       </c>
       <c r="D40" t="n">
-        <v>29.3249140214946</v>
+        <v>4.765298528492873</v>
       </c>
       <c r="E40" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F40" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>39.76165347068428</v>
+        <v>6.461268688986196</v>
       </c>
       <c r="D41" t="n">
-        <v>35.94924212257506</v>
+        <v>5.841751844918448</v>
       </c>
       <c r="E41" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F41" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>38.75169089743346</v>
+        <v>6.297149770832938</v>
       </c>
       <c r="D42" t="n">
-        <v>38.7093690890898</v>
+        <v>6.290272476977093</v>
       </c>
       <c r="E42" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F42" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>58.99845547043221</v>
+        <v>9.587249013945234</v>
       </c>
       <c r="D43" t="n">
-        <v>59.00832238420119</v>
+        <v>9.588852387432695</v>
       </c>
       <c r="E43" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F43" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>25.91168857331724</v>
+        <v>4.210649393164052</v>
       </c>
       <c r="D44" t="n">
-        <v>22.67930427888045</v>
+        <v>3.685386945318073</v>
       </c>
       <c r="E44" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F44" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>40.0523274140572</v>
+        <v>6.508503204784295</v>
       </c>
       <c r="D45" t="n">
-        <v>39.1636962144492</v>
+        <v>6.364100634847994</v>
       </c>
       <c r="E45" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F45" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>30.75313152467118</v>
+        <v>4.997383872759066</v>
       </c>
       <c r="D46" t="n">
-        <v>27.55036616339176</v>
+        <v>4.476934501551161</v>
       </c>
       <c r="E46" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F46" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>33.50411929799861</v>
+        <v>5.444419385924775</v>
       </c>
       <c r="D47" t="n">
-        <v>33.70244511201285</v>
+        <v>5.476647330702089</v>
       </c>
       <c r="E47" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F47" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>42.88348685021136</v>
+        <v>6.968566613159346</v>
       </c>
       <c r="D48" t="n">
-        <v>34.0357070872335</v>
+        <v>5.530802401675444</v>
       </c>
       <c r="E48" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F48" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>45.44894425923547</v>
+        <v>7.385453442125764</v>
       </c>
       <c r="D49" t="n">
-        <v>45.80636902918911</v>
+        <v>7.44353496724323</v>
       </c>
       <c r="E49" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F49" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>52.62482956785848</v>
+        <v>8.551534804777004</v>
       </c>
       <c r="D50" t="n">
-        <v>52.97795930841895</v>
+        <v>8.608918387618079</v>
       </c>
       <c r="E50" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F50" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>22.2047934325612</v>
+        <v>3.608278932791194</v>
       </c>
       <c r="D51" t="n">
-        <v>21.89981582034473</v>
+        <v>3.558720070806018</v>
       </c>
       <c r="E51" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F51" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>81.63413579678436</v>
+        <v>13.26554706697746</v>
       </c>
       <c r="D52" t="n">
-        <v>68.5771988312915</v>
+        <v>11.14379481008487</v>
       </c>
       <c r="E52" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F52" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>36.84874495747128</v>
+        <v>5.987921055589084</v>
       </c>
       <c r="D53" t="n">
-        <v>37.23993736040726</v>
+        <v>6.05148982106618</v>
       </c>
       <c r="E53" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F53" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>85.4958883297631</v>
+        <v>13.89308185358651</v>
       </c>
       <c r="D54" t="n">
-        <v>72.17100268194918</v>
+        <v>11.72778793581674</v>
       </c>
       <c r="E54" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F54" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>22.36122879115752</v>
+        <v>3.633699678563097</v>
       </c>
       <c r="D55" t="n">
-        <v>15.76900801175926</v>
+        <v>2.562463801910881</v>
       </c>
       <c r="E55" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F55" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>9.659380497501726</v>
+        <v>1.56964933084403</v>
       </c>
       <c r="D56" t="n">
-        <v>9.625199503150517</v>
+        <v>1.564094919261959</v>
       </c>
       <c r="E56" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F56" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>24.42735117834011</v>
+        <v>3.969444566480268</v>
       </c>
       <c r="D57" t="n">
-        <v>24.91958584947173</v>
+        <v>4.049432700539156</v>
       </c>
       <c r="E57" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F57" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>21.15231072453556</v>
+        <v>3.437250492737028</v>
       </c>
       <c r="D58" t="n">
-        <v>21.39975713156132</v>
+        <v>3.477460533878715</v>
       </c>
       <c r="E58" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F58" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>5.34286374886876</v>
+        <v>0.8682153591911735</v>
       </c>
       <c r="D59" t="n">
-        <v>4.965465384478273</v>
+        <v>0.8068881249777194</v>
       </c>
       <c r="E59" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F59" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>42.31700742462803</v>
+        <v>6.876513706502055</v>
       </c>
       <c r="D60" t="n">
-        <v>42.84859715741959</v>
+        <v>6.962897038080683</v>
       </c>
       <c r="E60" t="n">
-        <v>23.55600329676586</v>
+        <v>3.827850535724453</v>
       </c>
       <c r="F60" t="n">
-        <v>17.57306247170321</v>
+        <v>2.855622651651771</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
